--- a/docs/examples/TSWorkData/Reports/업무대장_전체_예제.xlsx
+++ b/docs/examples/TSWorkData/Reports/업무대장_전체_예제.xlsx
@@ -88,7 +88,7 @@
     <x:t>원본 업무</x:t>
   </x:si>
   <x:si>
-    <x:t>TS-2026-0004</x:t>
+    <x:t>TS-2026-09-0001</x:t>
   </x:si>
   <x:si>
     <x:t>완료</x:t>
@@ -133,7 +133,7 @@
     <x:t>정기점검</x:t>
   </x:si>
   <x:si>
-    <x:t>TS-2026-0001</x:t>
+    <x:t>TS-2026-10-0001</x:t>
   </x:si>
   <x:si>
     <x:t>높음</x:t>
@@ -179,7 +179,7 @@
     <x:t>조명, 오판정</x:t>
   </x:si>
   <x:si>
-    <x:t>TS-2026-0003</x:t>
+    <x:t>TS-2026-10-0003</x:t>
   </x:si>
   <x:si>
     <x:t>접수</x:t>
@@ -191,10 +191,10 @@
     <x:t>[모니터링] 2라인 OCR 오판정 증가 (조명 열화)</x:t>
   </x:si>
   <x:si>
-    <x:t>TS-2026-0001 조치 후 7일간 재발 여부 확인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TS-2026-0002</x:t>
+    <x:t>TS-2026-10-0001 조치 후 7일간 재발 여부 확인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TS-2026-10-0002</x:t>
   </x:si>
   <x:si>
     <x:t>긴급</x:t>
@@ -243,7 +243,7 @@
     <x:t>재연결, 통신</x:t>
   </x:si>
   <x:si>
-    <x:t>TS-2026-0005</x:t>
+    <x:t>TS-2026-10-0004</x:t>
   </x:si>
   <x:si>
     <x:t>조치 중</x:t>
@@ -273,7 +273,7 @@
     <x:t>바코드</x:t>
   </x:si>
   <x:si>
-    <x:t>TS-2026-0006</x:t>
+    <x:t>TS-2026-10-0005</x:t>
   </x:si>
   <x:si>
     <x:t>낮음</x:t>
@@ -796,7 +796,7 @@
   <x:dimension ref="A1:W7"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="13.600625" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="16.370625" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="11.535425" style="1" customWidth="1"/>
     <x:col min="3" max="3" width="11.620625" style="1" customWidth="1"/>
     <x:col min="4" max="4" width="11.535425" style="1" customWidth="1"/>
@@ -811,7 +811,7 @@
     <x:col min="13" max="20" width="40.710625" style="0" customWidth="1"/>
     <x:col min="21" max="21" width="16.285425" style="0" customWidth="1"/>
     <x:col min="22" max="22" width="14.360625" style="0" customWidth="1"/>
-    <x:col min="23" max="23" width="14.335425" style="0" customWidth="1"/>
+    <x:col min="23" max="23" width="16.370625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:23">
